--- a/docs/M5.5_P4-3.2_审核清单_批1.xlsx
+++ b/docs/M5.5_P4-3.2_审核清单_批1.xlsx
@@ -656,7 +656,7 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>无向图的邻接矩阵关于主对角线对称，每条边会在矩阵中对应两个非零元素，因此非零元素个数为 2e。A 项只考虑了每条边一个元素，忽略了无向图的对称性；C 项和 D 项均不符合邻接矩阵中边与元素个数的对应关系。常见易错点是混淆有向图与无向图的邻接矩阵非零元素个数。复习建议：掌握邻接矩阵的空间复杂度 O(n^2) 以及无向图、有向图、带权图在矩阵中的表示差异。</t>
+          <t>无向图的邻接矩阵关于主对角线对称，每条边会在矩阵中对应两个非零元素，因此非零元素个数为 2e。B 项只考虑了每条边一个元素，忽略了无向图的对称性；A 项和 D 项均不符合邻接矩阵中边与元素个数的对应关系。常见易错点是混淆有向图与无向图的邻接矩阵非零元素个数。复习建议：掌握邻接矩阵的空间复杂度 O(n^2) 以及无向图、有向图、带权图在矩阵中的表示差异。</t>
         </is>
       </c>
       <c r="O2" s="8" t="n"/>
@@ -726,7 +726,7 @@
       </c>
       <c r="N3" s="7" t="inlineStr">
         <is>
-          <t>邻接表便于统计出度，因为每个顶点的边表记录了它指向的邻接点；但统计入度需要遍历整个邻接表。建立逆邻接表后，每个顶点的边表记录的是指向该顶点的边，因此可以高效统计入度。A 项邻接矩阵虽然也能统计入度，但空间开销大且并非针对邻接表的改进；C 项排序不能直接得到入度；D 项栈与入度统计无关。常见易错点是把邻接表和逆邻接表的功能混淆。复习建议：理解邻接表、逆邻接表、十字链表和邻接多重表的适用场景。</t>
+          <t>邻接表便于统计出度，因为每个顶点的边表记录了它指向的邻接点；但统计入度需要遍历整个邻接表。建立逆邻接表后，每个顶点的边表记录的是指向该顶点的边，因此可以高效统计入度。A 项邻接矩阵虽然也能统计入度，但空间开销大且并非针对邻接表的改进；C 项排序不能直接得到入度；B 项栈与入度统计无关。常见易错点是把邻接表和逆邻接表的功能混淆。复习建议：理解邻接表、逆邻接表、十字链表和邻接多重表的适用场景。</t>
         </is>
       </c>
       <c r="O3" s="8" t="n"/>
@@ -796,7 +796,7 @@
       </c>
       <c r="N4" s="7" t="inlineStr">
         <is>
-          <t>邻接矩阵可以直接通过下标访问判断两顶点之间是否有边，时间复杂度为 O(1)；邻接表需要遍历对应顶点的边表，最坏为 O(n)。A 项说反了，邻接矩阵更适合稠密图，邻接表更适合稀疏图；B 项错误，邻接矩阵空间复杂度为 O(n^2)，与边数无关，邻接表空间复杂度为 O(n+e)，与顶点数和边数都有关；D 项错误，无向图的每条边在邻接表中通常存储两次。常见易错点是混淆两种存储结构的适用场景和复杂度。复习建议：从空间、判断边、遍历邻接点等角度对比邻接矩阵和邻接表。</t>
+          <t>邻接矩阵可以直接通过下标访问判断两顶点之间是否有边，时间复杂度为 O(1)；邻接表需要遍历对应顶点的边表，最坏为 O(n)。C 项说反了，邻接矩阵更适合稠密图，邻接表更适合稀疏图；D 项错误，邻接矩阵空间复杂度为 O(n^2)，与边数无关，邻接表空间复杂度为 O(n+e)，与顶点数和边数都有关；B 项错误，无向图的每条边在邻接表中通常存储两次。常见易错点是混淆两种存储结构的适用场景和复杂度。复习建议：从空间、判断边、遍历邻接点等角度对比邻接矩阵和邻接表。</t>
         </is>
       </c>
       <c r="O4" s="8" t="n"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>正确答案为A。二叉树的定义强调每个结点至多有两棵子树，并且左、右子树严格区分，次序不能颠倒。B项错误，度为2的有序树并不要求每个结点至多两棵子树，也不一定区分左右空子树，与二叉树定义不同。C项错误，二叉树可以只有一个根结点，所有结点的度都为0。D项错误，二叉树中允许存在度为1的结点。常见易错点是把普通有序树与二叉树混为一谈，忽略左右子树的有序性。复习时应紧扣二叉树的递归定义，并注意与度为2的树进行对比。</t>
+          <t>正确答案为B。二叉树的定义强调每个结点至多有两棵子树，并且左、右子树严格区分，次序不能颠倒。C项错误，度为2的有序树并不要求每个结点至多两棵子树，也不一定区分左右空子树，与二叉树定义不同。A项错误，二叉树可以只有一个根结点，所有结点的度都为0。D项错误，二叉树中允许存在度为1的结点。常见易错点是把普通有序树与二叉树混为一谈，忽略左右子树的有序性。复习时应紧扣二叉树的递归定义，并注意与度为2的树进行对比。</t>
         </is>
       </c>
       <c r="O5" s="8" t="n"/>
@@ -936,7 +936,7 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>正确答案为A。设二叉树结点总数为n，边数为e，则n = n0 + n1 + n2，且除根外每个结点对应一条入边，所以e = n - 1。又因为边数等于各结点度数之和，即e = n1 + 2n2，联立可得n0 = n2 + 1。B、C、D均不符合推导结果。常见易错点是把完全二叉树或满二叉树的性质误用到一般二叉树，或忽略度为1的结点对边数的贡献。复习时建议掌握结点数、边数与度数之间的计数关系，并会用该关系推导叶子结点公式。</t>
+          <t>正确答案为B。设二叉树结点总数为n，边数为e，则n = n0 + n1 + n2，且除根外每个结点对应一条入边，所以e = n - 1。又因为边数等于各结点度数之和，即e = n1 + 2n2，联立可得n0 = n2 + 1。B、C、D均不符合推导结果。常见易错点是把完全二叉树或满二叉树的性质误用到一般二叉树，或忽略度为1的结点对边数的贡献。复习时建议掌握结点数、边数与度数之间的计数关系，并会用该关系推导叶子结点公式。</t>
         </is>
       </c>
       <c r="O6" s="8" t="n"/>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="N7" s="7" t="inlineStr">
         <is>
-          <t>正确答案为C。根据二叉树性质，叶子结点数n0与度为2的结点数n2满足n0 = n2 + 1。题中n2 = 10，因此n0 = 11。度为1的结点数5不影响叶子结点数的计算，只影响结点总数。A项误用n2 - 1，B项误认为叶子数等于度为2的结点数，D项把度为1的结点也计入。常见易错点是看到多个条件后乱用公式，或把总结点数与叶子结点数混淆。复习时应熟记n0 = n2 + 1，并明确该公式对任意非空二叉树都成立。</t>
+          <t>正确答案为B。根据二叉树性质，叶子结点数n0与度为2的结点数n2满足n0 = n2 + 1。题中n2 = 10，因此n0 = 11。度为1的结点数5不影响叶子结点数的计算，只影响结点总数。A项误用n2 - 1，D项误认为叶子数等于度为2的结点数，C项把度为1的结点也计入。常见易错点是看到多个条件后乱用公式，或把总结点数与叶子结点数混淆。复习时应熟记n0 = n2 + 1，并明确该公式对任意非空二叉树都成立。</t>
         </is>
       </c>
       <c r="O7" s="8" t="n"/>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>正确答案是B。线性表是由n个数据元素组成的有限序列，其逻辑特征是元素之间为一对一关系，除第一个元素外每个元素有且仅有一个直接前驱，除最后一个元素外每个元素有且仅有一个直接后继。A错误，线性表只要求元素属于同一数据对象，并不要求各元素占用空间完全相同，例如顺序表中元素类型相同但逻辑上并不强制存储空间大小一致这一说法本身表述不当。C错误，线性表是逻辑结构，既可用顺序存储也可用链式存储。D错误，线性表长度可以动态变化，插入删除操作会改变表长。常见易错点是把逻辑结构与存储结构混为一谈，复习时应区分线性表的逻辑定义与两种实现方式。</t>
+          <t>正确答案是A。线性表是由n个数据元素组成的有限序列，其逻辑特征是元素之间为一对一关系，除第一个元素外每个元素有且仅有一个直接前驱，除最后一个元素外每个元素有且仅有一个直接后继。A错误，线性表只要求元素属于同一数据对象，并不要求各元素占用空间完全相同，例如顺序表中元素类型相同但逻辑上并不强制存储空间大小一致这一说法本身表述不当。C错误，线性表是逻辑结构，既可用顺序存储也可用链式存储。D错误，线性表长度可以动态变化，插入删除操作会改变表长。常见易错点是把逻辑结构与存储结构混为一谈，复习时应区分线性表的逻辑定义与两种实现方式。</t>
         </is>
       </c>
       <c r="O8" s="8" t="n"/>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>正确答案是C。顺序表在第i个位置插入元素时，原第i个到第n个元素都要后移一位，共移动n-i+1个元素。当i=n+1时表示在表尾插入，移动0个元素，代入公式得n-(n+1)+1=0，符合实际。A、B、D均不正确，其中B的n-i是删除第i个元素时需要移动的元素个数，容易与插入混淆。常见易错点在于插入与删除的移动次数公式记反，以及忽略表尾插入和表头插入这两种边界情况。复习建议是结合具体例子（如n=5，i=1和i=6）逐一验证公式，并区分插入与删除的移动规律。</t>
+          <t>正确答案是D。顺序表在第i个位置插入元素时，原第i个到第n个元素都要后移一位，共移动n-i+1个元素。当i=n+1时表示在表尾插入，移动0个元素，代入公式得n-(n+1)+1=0，符合实际。A、B、D均不正确，其中B的n-i是删除第i个元素时需要移动的元素个数，容易与插入混淆。常见易错点在于插入与删除的移动次数公式记反，以及忽略表尾插入和表头插入这两种边界情况。复习建议是结合具体例子（如n=5，i=1和i=6）逐一验证公式，并区分插入与删除的移动规律。</t>
         </is>
       </c>
       <c r="O9" s="8" t="n"/>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>正确答案是B。链式存储的线性表通过指针链接结点，访问第k个元素必须从表头开始沿指针逐个查找，属于顺序存取，不能随机存取；但插入删除只需修改指针，不需移动大量元素。A错误，链式存储不具备随机存取特性。C错误，链式存储每个结点需额外存储指针域，存储密度低于顺序表。D错误，链式存储不要求连续空间，也无需预先分配固定大小。常见易错点是误认为链表也能随机访问，或混淆存储密度与空间利用率。复习时应重点比较顺序表与链表在存取方式、插入删除效率、空间开销上的差异。</t>
+          <t>正确答案是C。链式存储的线性表通过指针链接结点，访问第k个元素必须从表头开始沿指针逐个查找，属于顺序存取，不能随机存取；但插入删除只需修改指针，不需移动大量元素。A错误，链式存储不具备随机存取特性。C错误，链式存储每个结点需额外存储指针域，存储密度低于顺序表。D错误，链式存储不要求连续空间，也无需预先分配固定大小。常见易错点是误认为链表也能随机访问，或混淆存储密度与空间利用率。复习时应重点比较顺序表与链表在存取方式、插入删除效率、空间开销上的差异。</t>
         </is>
       </c>
       <c r="O10" s="8" t="n"/>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>正确答案是 A。顺序表插入元素时，若在第 i 个位置插入，需要将第 i 到第 n 个元素整体后移，移动次数为 n-i+1。等概率情况下 i 取 1 到 n+1，平均移动次数为 (1/(n+1))·Σ(n-i+1)=n/2。B 项 n 是最大移动次数，不是平均值；C 项 (n+1)/2 常与删除操作的平均移动次数混淆；D 项 n-1 没有理论依据。常见易错点是插入位置编号从 1 开始，且插入位置共有 n+1 种可能。复习建议：牢记插入平均移动 n/2、删除平均移动 (n-1)/2，并理解推导过程。</t>
+          <t>正确答案是 A。顺序表插入元素时，若在第 i 个位置插入，需要将第 i 到第 n 个元素整体后移，移动次数为 n-i+1。等概率情况下 i 取 1 到 n+1，平均移动次数为 (1/(n+1))·Σ(n-i+1)=n/2。B 项 n 是最大移动次数，不是平均值；D 项 (n+1)/2 常与删除操作的平均移动次数混淆；C 项 n-1 没有理论依据。常见易错点是插入位置编号从 1 开始，且插入位置共有 n+1 种可能。复习建议：牢记插入平均移动 n/2、删除平均移动 (n-1)/2，并理解推导过程。</t>
         </is>
       </c>
       <c r="O11" s="8" t="n"/>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>正确答案是 B。顺序表采用连续存储，只要知道首地址和下标，就能通过地址公式直接定位元素，因此随机访问时间复杂度为 O(1)。A 项错误，顺序表插入删除通常需要移动大量元素，效率低于链表；C 项错误，顺序表虽然要求连续空间，但可以通过重新分配更大空间并复制元素实现动态扩容；D 项错误，顺序表是顺序存储结构，不是链式存储。常见易错点是把逻辑相邻与物理相邻混淆。复习建议：从存储方式、访问方式、插入删除效率、空间分配四个维度对比顺序表和链表。</t>
+          <t>正确答案是 D。顺序表采用连续存储，只要知道首地址和下标，就能通过地址公式直接定位元素，因此随机访问时间复杂度为 O(1)。C 项错误，顺序表插入删除通常需要移动大量元素，效率低于链表；B 项错误，顺序表虽然要求连续空间，但可以通过重新分配更大空间并复制元素实现动态扩容；A 项错误，顺序表是顺序存储结构，不是链式存储。常见易错点是把逻辑相邻与物理相邻混淆。复习建议：从存储方式、访问方式、插入删除效率、空间分配四个维度对比顺序表和链表。</t>
         </is>
       </c>
       <c r="O12" s="8" t="n"/>
@@ -1426,7 +1426,7 @@
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>正确答案是 C。顺序表删除第 i 个元素时，需要将第 i+1 到第 n 个元素依次前移，移动次数为 n-i。本题 n=10，i=4，因此移动次数为 10-4=6。A 项 4 误把删除位置当作移动个数；B 项 5 可能是把下标从 0 开始计算导致的偏差；D 项 7 没有正确套用公式。常见易错点是删除位置编号从 1 开始，而移动元素个数为 n-i。复习建议：熟记删除操作移动次数公式，并通过画图模拟元素移动过程加深理解。</t>
+          <t>正确答案是 D。顺序表删除第 i 个元素时，需要将第 i+1 到第 n 个元素依次前移，移动次数为 n-i。本题 n=10，i=4，因此移动次数为 10-4=6。B 项 4 误把删除位置当作移动个数；C 项 5 可能是把下标从 0 开始计算导致的偏差；A 项 7 没有正确套用公式。常见易错点是删除位置编号从 1 开始，而移动元素个数为 n-i。复习建议：熟记删除操作移动次数公式，并通过画图模拟元素移动过程加深理解。</t>
         </is>
       </c>
       <c r="O13" s="8" t="n"/>
@@ -1566,7 +1566,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>正确答案是 C。带头结点的单链表中，头结点不存放有效数据（或数据域可另作他用），其 next 指向首元素结点，这样在表头插入或删除时无需特殊修改头指针，能与普通位置统一处理。A 错误，头结点数据域并非必须存放长度；B 错误，删除首元素结点只需修改头结点的 next，头指针 head 本身不变；D 表述不严谨，头结点确实多占一个结点空间，但该结点不属于数据元素，且“数据元素的空间”说法易引起歧义。常见易错点是把头结点与首元素结点混淆。复习建议：明确头指针、头结点、首元素结点的区别与联系。</t>
+          <t>正确答案是 A。带头结点的单链表中，头结点不存放有效数据（或数据域可另作他用），其 next 指向首元素结点，这样在表头插入或删除时无需特殊修改头指针，能与普通位置统一处理。A 错误，头结点数据域并非必须存放长度；B 错误，删除首元素结点只需修改头结点的 next，头指针 head 本身不变；D 表述不严谨，头结点确实多占一个结点空间，但该结点不属于数据元素，且“数据元素的空间”说法易引起歧义。常见易错点是把头结点与首元素结点混淆。复习建议：明确头指针、头结点、首元素结点的区别与联系。</t>
         </is>
       </c>
       <c r="O15" s="8" t="n"/>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>正确答案为 A。push(1)、push(2) 后栈为 [1,2]；pop() 弹出栈顶 2，栈变为 [1]；再 push(3)、push(4)、push(5)，栈自底向顶为 1,3,4,5。B 项忽略了 pop 操作，C 项误认为 1 也被弹出，D 项把栈顶到栈底顺序当成了栈底到栈顶顺序。常见易错点是混淆栈顶与栈底方向、忘记后进先出规则。复习建议：动手画出 top 指针变化过程，明确顺序栈中 top 指向栈顶元素、入栈先加指针再存值、出栈先取值再减指针。</t>
+          <t>正确答案为 C。push(1)、push(2) 后栈为 [1,2]；pop() 弹出栈顶 2，栈变为 [1]；再 push(3)、push(4)、push(5)，栈自底向顶为 1,3,4,5。A 项忽略了 pop 操作，B 项误认为 1 也被弹出，D 项把栈顶到栈底顺序当成了栈底到栈顶顺序。常见易错点是混淆栈顶与栈底方向、忘记后进先出规则。复习建议：动手画出 top 指针变化过程，明确顺序栈中 top 指向栈顶元素、入栈先加指针再存值、出栈先取值再减指针。</t>
         </is>
       </c>
       <c r="O16" s="8" t="n"/>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>正确答案为 C。链栈用单链表实现时，通常把表头作为栈顶，栈顶指针指向首结点，入栈相当于头插，出栈相当于删除首结点，两者均为 O(1)。A 项错误，链栈可以不带头结点，栈顶指针直接指向首元素结点；B 项错误，若在尾部操作需遍历找前驱，效率低；D 项错误，链栈虽一般不会栈满，但出栈前必须判断栈空。常见易错点是把链栈与顺序栈的栈顶位置混为一谈。复习建议：对比顺序栈与链栈的 top 含义、判空条件和基本操作实现。</t>
+          <t>正确答案为 C。链栈用单链表实现时，通常把表头作为栈顶，栈顶指针指向首结点，入栈相当于头插，出栈相当于删除首结点，两者均为 O(1)。D 项错误，链栈可以不带头结点，栈顶指针直接指向首元素结点；A 项错误，若在尾部操作需遍历找前驱，效率低；B 项错误，链栈虽一般不会栈满，但出栈前必须判断栈空。常见易错点是把链栈与顺序栈的栈顶位置混为一谈。复习建议：对比顺序栈与链栈的 top 含义、判空条件和基本操作实现。</t>
         </is>
       </c>
       <c r="O17" s="8" t="n"/>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>正确答案为A。由先序序列ABDECF可知根结点为A；在中序序列DBEAFC中，A左侧为DBE，右侧为FC，因此左子树中序为DBE、右子树中序为FC。左子树先序为BDE，根为B，中序DBE中B左侧为D、右侧为E，故左子树后序为DEB；右子树先序为CF，根为C，中序FC中C左侧为F，故右子树后序为FC。最终后序为DEB+F+C+A，即DEBFCA。错误选项B、C、D均是在左右子树划分或递归顺序上出现偏差，常见易错点是把先序根的位置与中序根的位置混淆，或忽略右子树只有一个结点时的顺序。复习建议：熟练掌握由两种遍历序列唯一确定二叉树的方法，并多做递归划分练习。</t>
+          <t>正确答案为A。由先序序列ABDECF可知根结点为A；在中序序列DBEAFC中，A左侧为DBE，右侧为FC，因此左子树中序为DBE、右子树中序为FC。左子树先序为BDE，根为B，中序DBE中B左侧为D、右侧为E，故左子树后序为DEB；右子树先序为CF，根为C，中序FC中C左侧为F，故右子树后序为FC。最终后序为DEB+F+C+A，即DEBFCA。错误选项D、C、D均是在左右子树划分或递归顺序上出现偏差，常见易错点是把先序根的位置与中序根的位置混淆，或忽略右子树只有一个结点时的顺序。复习建议：熟练掌握由两种遍历序列唯一确定二叉树的方法，并多做递归划分练习。</t>
         </is>
       </c>
       <c r="O18" s="8" t="n"/>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>正确答案是C。直接插入排序在每一趟中只是将当前元素插入到前面已排好序的子序列中，已有序子序列中的元素位置仍可能因后续元素的插入而整体后移，因此不能保证每趟至少有一个元素到达最终位置。冒泡排序每趟可将最大或最小元素送到最终位置，快速排序每趟划分可将枢轴元素放到最终位置，简单选择排序每趟可选择最小元素放到最终位置，三者均具备该性质。常见易错点是把“局部有序”误认为“最终位置确定”，复习时应重点区分各排序算法每趟操作后元素位置的确定性。</t>
+          <t>正确答案是D。直接插入排序在每一趟中只是将当前元素插入到前面已排好序的子序列中，已有序子序列中的元素位置仍可能因后续元素的插入而整体后移，因此不能保证每趟至少有一个元素到达最终位置。冒泡排序每趟可将最大或最小元素送到最终位置，快速排序每趟划分可将枢轴元素放到最终位置，简单选择排序每趟可选择最小元素放到最终位置，三者均具备该性质。常见易错点是把“局部有序”误认为“最终位置确定”，复习时应重点区分各排序算法每趟操作后元素位置的确定性。</t>
         </is>
       </c>
       <c r="O20" s="8" t="n"/>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>正确答案是C。堆排序在调整堆的过程中可能将关键字相同的元素交换到相对次序相反的位置，因此是不稳定排序，无法保证排序后 5 仍位于 5' 之前。直接插入排序、归并排序和冒泡排序都是稳定排序，在关键字相等时不会改变元素的相对次序。常见易错点是把“时间复杂度为O(nlogn)”与“稳定”混为一谈，误认为归并排序和堆排序都稳定。复习建议是熟记常见排序算法的稳定性：稳定的有插入、冒泡、归并、基数排序；不稳定的有选择、快速、希尔、堆排序。</t>
+          <t>正确答案是B。堆排序在调整堆的过程中可能将关键字相同的元素交换到相对次序相反的位置，因此是不稳定排序，无法保证排序后 5 仍位于 5' 之前。直接插入排序、归并排序和冒泡排序都是稳定排序，在关键字相等时不会改变元素的相对次序。常见易错点是把“时间复杂度为O(nlogn)”与“稳定”混为一谈，误认为归并排序和堆排序都稳定。复习建议是熟记常见排序算法的稳定性：稳定的有插入、冒泡、归并、基数排序；不稳定的有选择、快速、希尔、堆排序。</t>
         </is>
       </c>
       <c r="O21" s="8" t="n"/>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>2026-10-12T16:00:47+00:00</t>
+          <t>2026-10-14T07:26:58+00:00</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2269,7 @@
       </c>
       <c r="B9" s="13" t="inlineStr">
         <is>
-          <t>200061b6ee89aba50becb5f3d12a5e76582c19db32302cdb1593e56a3d67dde2</t>
+          <t>1ea3e486a644e46956b4be309ac9880bab1af51539f3ce3591acf9918db33599</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>2026-10-12T00:00:00+00:00</t>
+          <t>2026-10-14T07:26:59+00:00</t>
         </is>
       </c>
     </row>

--- a/docs/M5.5_P4-3.2_审核清单_批1.xlsx
+++ b/docs/M5.5_P4-3.2_审核清单_批1.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="H2" s="7" t="inlineStr">
         <is>
-          <t>对于一个含有 n 个顶点、e 条边的无向图，若采用邻接矩阵存储，则矩阵中非零元素的个数通常为（ ）。</t>
+          <t>对于一个含有n个顶点、e条边的简单无权无向图（无自环、无重边），邻接矩阵用1表示有边、0表示无边，则矩阵中非零元素的个数为（ ）。</t>
         </is>
       </c>
       <c r="I2" s="7" t="inlineStr">
@@ -656,11 +656,19 @@
       </c>
       <c r="N2" s="7" t="inlineStr">
         <is>
-          <t>无向图的邻接矩阵关于主对角线对称，每条边会在矩阵中对应两个非零元素，因此非零元素个数为 2e。B 项只考虑了每条边一个元素，忽略了无向图的对称性；A 项和 D 项均不符合邻接矩阵中边与元素个数的对应关系。常见易错点是混淆有向图与无向图的邻接矩阵非零元素个数。复习建议：掌握邻接矩阵的空间复杂度 O(n^2) 以及无向图、有向图、带权图在矩阵中的表示差异。</t>
-        </is>
-      </c>
-      <c r="O2" s="8" t="n"/>
-      <c r="P2" s="7" t="n"/>
+          <t>正确答案为C。每条无向边连接两个不同顶点u、v，矩阵中A[u,v]和A[v,u]各为1；无自环使主对角线为0，无重边使不同边的矩阵位置不重复。因此e条边恰好对应2e个非零元素。A项n+e错误地把顶点数加入计数；B项e漏计了对称位置；D项n²-e没有反映每条边占两个位置。易错点是混淆有向图与无向图的表示。复习时可画出三个顶点、一条边的0/1矩阵，直接数出两个1。</t>
+        </is>
+      </c>
+      <c r="O2" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P2" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；补足简单无权图及0/1矩阵条件，排除自环和零权边歧义。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -866,11 +874,19 @@
       </c>
       <c r="N5" s="7" t="inlineStr">
         <is>
-          <t>正确答案为B。二叉树的定义强调每个结点至多有两棵子树，并且左、右子树严格区分，次序不能颠倒。C项错误，度为2的有序树并不要求每个结点至多两棵子树，也不一定区分左右空子树，与二叉树定义不同。A项错误，二叉树可以只有一个根结点，所有结点的度都为0。D项错误，二叉树中允许存在度为1的结点。常见易错点是把普通有序树与二叉树混为一谈，忽略左右子树的有序性。复习时应紧扣二叉树的递归定义，并注意与度为2的树进行对比。</t>
-        </is>
-      </c>
-      <c r="O5" s="8" t="n"/>
-      <c r="P5" s="7" t="n"/>
+          <t>正确答案为B。二叉树每个结点最多有两个孩子，且孩子具有固定的左、右位置；只有一个孩子时也必须区分左孩子或右孩子。A项错误，只有根结点的二叉树不存在度为2的结点。C项错误，普通有序树的度为2意味着最大结点度为2，但唯一孩子的次序不能单独表达二叉树的左槽或右槽位置，因此两种结构并不等同。D项错误，二叉树允许度为1的结点。易错点是把树的度误解为每个结点的度。复习时比较只有左孩子和只有右孩子的两棵二叉树。</t>
+        </is>
+      </c>
+      <c r="O5" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P5" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；纠正树的度定义，并以单孩子左/右槽区分二叉树和普通有序树。</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -936,11 +952,19 @@
       </c>
       <c r="N6" s="7" t="inlineStr">
         <is>
-          <t>正确答案为B。设二叉树结点总数为n，边数为e，则n = n0 + n1 + n2，且除根外每个结点对应一条入边，所以e = n - 1。又因为边数等于各结点度数之和，即e = n1 + 2n2，联立可得n0 = n2 + 1。B、C、D均不符合推导结果。常见易错点是把完全二叉树或满二叉树的性质误用到一般二叉树，或忽略度为1的结点对边数的贡献。复习时建议掌握结点数、边数与度数之间的计数关系，并会用该关系推导叶子结点公式。</t>
-        </is>
-      </c>
-      <c r="O6" s="8" t="n"/>
-      <c r="P6" s="7" t="n"/>
+          <t>正确答案为B。令度为1的结点数为n1，总结点数N=n0+n1+n2。非空树的边数为N-1，又等于各结点孩子数之和n1+2n2，联立得到n0=n2+1。A项把加1错成减1，C项漏掉根结点对应的差1，D项错误地重复计算度为2结点的贡献。只有根的树中n0=1、n2=0，也能检验B成立而其余选项不成立。易错点是混淆结点总数与边数。复习时应理解计数推导，不要仅机械记忆公式。</t>
+        </is>
+      </c>
+      <c r="O6" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；纠正把正确B列为错误项的矛盾，错误项为A/C/D。</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
@@ -1076,11 +1100,19 @@
       </c>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>正确答案是A。线性表是由n个数据元素组成的有限序列，其逻辑特征是元素之间为一对一关系，除第一个元素外每个元素有且仅有一个直接前驱，除最后一个元素外每个元素有且仅有一个直接后继。A错误，线性表只要求元素属于同一数据对象，并不要求各元素占用空间完全相同，例如顺序表中元素类型相同但逻辑上并不强制存储空间大小一致这一说法本身表述不当。C错误，线性表是逻辑结构，既可用顺序存储也可用链式存储。D错误，线性表长度可以动态变化，插入删除操作会改变表长。常见易错点是把逻辑结构与存储结构混为一谈，复习时应区分线性表的逻辑定义与两种实现方式。</t>
-        </is>
-      </c>
-      <c r="O8" s="8" t="n"/>
-      <c r="P8" s="7" t="n"/>
+          <t>正确答案为A。线性表的逻辑结构是一对一关系：除首元素外，每个元素有唯一直接前驱；除尾元素外，每个元素有唯一直接后继。B项错误，同一逻辑线性表可以采用顺序存储或链式存储。C项错误，插入或删除会改变表长，有限序列不等于长度永远固定。D项错误，逻辑结构并不以每个元素占用相同字节数作为定义条件，具体存储实现另有约束；常规顺序表可使用固定步长槽位。易错点是把逻辑结构与物理布局混为一谈。复习时分别描述线性表的逻辑特征和实现方式。</t>
+        </is>
+      </c>
+      <c r="O8" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；重写B/C/D映射，澄清逻辑定义与顺序表固定槽位。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1146,11 +1178,19 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>正确答案是D。顺序表在第i个位置插入元素时，原第i个到第n个元素都要后移一位，共移动n-i+1个元素。当i=n+1时表示在表尾插入，移动0个元素，代入公式得n-(n+1)+1=0，符合实际。A、B、D均不正确，其中B的n-i是删除第i个元素时需要移动的元素个数，容易与插入混淆。常见易错点在于插入与删除的移动次数公式记反，以及忽略表尾插入和表头插入这两种边界情况。复习建议是结合具体例子（如n=5，i=1和i=6）逐一验证公式，并区分插入与删除的移动规律。</t>
-        </is>
-      </c>
-      <c r="O9" s="8" t="n"/>
-      <c r="P9" s="7" t="n"/>
+          <t>正确答案为D。在第i个位置插入时，原第i至第n个元素都需后移，闭区间包含n-i+1项。A项n-i是删除第i项时的移动数，不是插入移动数；B项n-i-1少算两项，尾插时甚至为负；C项i把位置编号当作移动数量。代入i=1需移动n项，i=n+1需移动0项，两端都验证D。易错点是混淆插入和删除的计数区间。复习时标出需要移动的第一个与最后一个元素，再计算闭区间长度。</t>
+        </is>
+      </c>
+      <c r="O9" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；错误项改A/B/C，删除移动数引用对应A。</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -1216,11 +1256,19 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>正确答案是C。链式存储的线性表通过指针链接结点，访问第k个元素必须从表头开始沿指针逐个查找，属于顺序存取，不能随机存取；但插入删除只需修改指针，不需移动大量元素。A错误，链式存储不具备随机存取特性。C错误，链式存储每个结点需额外存储指针域，存储密度低于顺序表。D错误，链式存储不要求连续空间，也无需预先分配固定大小。常见易错点是误认为链表也能随机访问，或混淆存储密度与空间利用率。复习时应重点比较顺序表与链表在存取方式、插入删除效率、空间开销上的差异。</t>
-        </is>
-      </c>
-      <c r="O10" s="8" t="n"/>
-      <c r="P10" s="7" t="n"/>
+          <t>正确答案为C。常规链式线性表按指针逐结点访问，查第k项需顺序走链，不能像顺序表一样由下标直接定位。已知插入位置或删除所需前驱时，链接修改只需O(1)，不必搬移后续大量元素；但寻找位置或前驱仍可能O(n)。A项错误，结点不要求预先分配连续空间；B项错误，指针域增加额外开销，存储密度通常低于顺序表；D项错误，虽然修改链接不需移动元素，但不能随机存取。易错点是忽略定位成本。复习时将查找位置与执行链接修改分开分析。</t>
+        </is>
+      </c>
+      <c r="O10" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；修正A/B/D引用，区分定位成本与已知前驱后的常数链接修改。</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -1256,7 +1304,7 @@
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>在一个长度为 n 的顺序表中，若要在第 i 个位置（1 ≤ i ≤ n+1）插入一个新元素，在等概率情况下，平均需要移动的元素个数约为多少？</t>
+          <t>在长度为n的顺序表中，向第i个位置（1≤i≤n+1）插入新元素。若n+1个插入位置等概率且仅统计既有元素的后移次数，平均移动次数的精确值是多少？</t>
         </is>
       </c>
       <c r="I11" s="7" t="inlineStr">
@@ -1286,11 +1334,19 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>正确答案是 A。顺序表插入元素时，若在第 i 个位置插入，需要将第 i 到第 n 个元素整体后移，移动次数为 n-i+1。等概率情况下 i 取 1 到 n+1，平均移动次数为 (1/(n+1))·Σ(n-i+1)=n/2。B 项 n 是最大移动次数，不是平均值；D 项 (n+1)/2 常与删除操作的平均移动次数混淆；C 项 n-1 没有理论依据。常见易错点是插入位置编号从 1 开始，且插入位置共有 n+1 种可能。复习建议：牢记插入平均移动 n/2、删除平均移动 (n-1)/2，并理解推导过程。</t>
-        </is>
-      </c>
-      <c r="O11" s="8" t="n"/>
-      <c r="P11" s="7" t="n"/>
+          <t>正确答案为A。插入位置i对应n-i+1次后移，全部n+1个位置的移动次数依次为n、n-1、直到0。总次数为n(n+1)/2，除以位置数n+1得精确期望n/2。B项n是最大移动次数；C项n-1不是平均值；D项(n+1)/2比精确值多1/2。以n=5为例，(5+4+3+2+1+0)/6=2.5。易错点是遗漏表尾这个无需移动的位置。复习时区分插入的n+1种位置与删除的n种位置。</t>
+        </is>
+      </c>
+      <c r="O11" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；要求精确期望，消除约为使两个选项近似成立的问题。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1466,7 +1522,7 @@
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>在一个不带头结点的单链表中，已知指针 p 指向某个结点（非首结点、非尾结点），若要在 p 所指结点之前插入一个新结点 s，且要求时间复杂度为 O(1)，下列做法中正确的是（ ）。</t>
+          <t>在不带头结点的单链表中，指针p指向非首、非尾结点。新结点s存有待插入元素，数据域大小固定且允许O(1)交换。只要求值序列中在p原来存储的元素之前插入新元素，不要求保持元素所在结点的地址身份。哪种操作可在O(1)内完成？</t>
         </is>
       </c>
       <c r="I14" s="7" t="inlineStr">
@@ -1496,11 +1552,19 @@
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>正确答案是 B。在不带头结点的单链表中，若只给指向某结点的指针 p，要在 p 之前插入结点且要求 O(1)，常规做法无法直接找到前驱，因此可采用“偷梁换柱”法：把 s 插到 p 之后，再交换 p 与 s 的数据域，逻辑上等价于在 p 之前插入。A 需要遍历找前驱，时间复杂度为 O(n)，不符合要求；C 会使 p 的后继丢失，且插入位置错误；D 先执行 p-&gt;next=s 后，s-&gt;next=p-&gt;next 实际指向 s 自身，形成自环。常见易错点是忽略“不带头结点”和“O(1)”两个限制。复习建议：熟练掌握带头结点与不带头结点插入操作的差异，并理解数据域交换技巧。</t>
-        </is>
-      </c>
-      <c r="O14" s="8" t="n"/>
-      <c r="P14" s="7" t="n"/>
+          <t>正确答案为B。设p原值为x、s原值为y，原链为q→p(x)→t。先将s接到p后得到q→p(x)→s(y)→t，再交换固定大小数据域，得到q→p(y)→s(x)→t，值序列由x变为y,x，满足题目允许的逻辑插入。A项让p与s相互指向形成环，并断开原后继；C项物理前插正确，但遍历找前驱为O(n)，不满足时间要求；D项使s.next指向s形成自环。易错点是混淆值序列与结点身份。复习时需明确该技巧不保证新结点s的地址出现在p之前。</t>
+        </is>
+      </c>
+      <c r="O14" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；明确逻辑插入、固定大小可交换数据域及不保留地址身份，纠正A/C解释。</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1551,7 +1615,7 @@
       </c>
       <c r="K15" s="7" t="inlineStr">
         <is>
-          <t>C. 带头结点的单链表一定比不带头结点的单链表多占用一个数据元素的空间</t>
+          <t>C. 计算线性表有效数据元素的个数时，必须将头结点计入</t>
         </is>
       </c>
       <c r="L15" s="7" t="inlineStr">
@@ -1566,11 +1630,19 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>正确答案是 A。带头结点的单链表中，头结点不存放有效数据（或数据域可另作他用），其 next 指向首元素结点，这样在表头插入或删除时无需特殊修改头指针，能与普通位置统一处理。A 错误，头结点数据域并非必须存放长度；B 错误，删除首元素结点只需修改头结点的 next，头指针 head 本身不变；D 表述不严谨，头结点确实多占一个结点空间，但该结点不属于数据元素，且“数据元素的空间”说法易引起歧义。常见易错点是把头结点与首元素结点混淆。复习建议：明确头指针、头结点、首元素结点的区别与联系。</t>
-        </is>
-      </c>
-      <c r="O15" s="8" t="n"/>
-      <c r="P15" s="7" t="n"/>
+          <t>正确答案为A。头结点位于首元素结点之前，表头插入或删除首元素都可通过修改前驱的next链接完成，因此与其他位置统一处理。B项错误，头结点数据域可以不用或另作他用，并非一定存长度。C项错误，头结点不是线性表的有效数据元素，不计入表长。D项错误，删除首元素时改变head所指头结点的next，head仍指向原头结点。头结点会占物理存储空间，但这与有效元素计数不同。易错点是混淆头指针、头结点和首元素结点，复习时应分别画出三者关系。</t>
+        </is>
+      </c>
+      <c r="O15" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P15" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；把C换成明确错误的有效元素计数命题，纠正B/C/D解释。</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -1780,11 +1852,19 @@
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>正确答案为A。由先序序列ABDECF可知根结点为A；在中序序列DBEAFC中，A左侧为DBE，右侧为FC，因此左子树中序为DBE、右子树中序为FC。左子树先序为BDE，根为B，中序DBE中B左侧为D、右侧为E，故左子树后序为DEB；右子树先序为CF，根为C，中序FC中C左侧为F，故右子树后序为FC。最终后序为DEB+F+C+A，即DEBFCA。错误选项D、C、D均是在左右子树划分或递归顺序上出现偏差，常见易错点是把先序根的位置与中序根的位置混淆，或忽略右子树只有一个结点时的顺序。复习建议：熟练掌握由两种遍历序列唯一确定二叉树的方法，并多做递归划分练习。</t>
-        </is>
-      </c>
-      <c r="O18" s="8" t="n"/>
-      <c r="P18" s="7" t="n"/>
+          <t>正确答案为A。先序ABDECF的根是A，中序DBEAFC以A分为DBE和FC。左子树先序BDE、中序DBE，根B的左孩子为D、右孩子为E，因此后序为DEB。右子树先序CF、中序FC，根C只有左孩子F，后序为FC。整树后序是DEB+FC+A，即DEBFCA。B项将左子树后序错写成DBE，C项错写成EDB，D项将右子树后序错写成CF。易错点是把根在先序与后序中的位置混淆。复习时应先按中序划分左右子树，再分别按后序规则连接。</t>
+        </is>
+      </c>
+      <c r="O18" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；逐项解释B/C/D，准确写C只有左孩子F，移除重复D和错误结点数量。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1845,16 +1925,24 @@
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>正确答案为C。后序序列CDBGFEA的最后一个结点A为根；在中序序列CBDAGFE中，A左侧为CBD，右侧为GFE，故左子树中序CBD、右子树中序GFE。左子树后序为CDB，根为B，中序CBD中B左侧为C、右侧为D，故左子树先序为BCD；右子树后序为GFE，根为E，中序GFE中E左侧为GF，故右子树先序为EFG。整棵树先序为A+BCD+EFG，即ABDCEFG。错误选项A、B、D分别错在左右子树划分、结点顺序或右子树内部顺序。常见易错点是由后序确定根后，未正确利用中序划分左右子树。复习建议：牢记后序最后为根、中序根左为左子树、根右为右子树，并反复练习重建二叉树。</t>
-        </is>
-      </c>
-      <c r="O19" s="8" t="n"/>
-      <c r="P19" s="7" t="n"/>
+          <t>正确答案为A。后序遍历CDBGFEA的最后一个结点A是根。中序遍历CBDAGFE以A划分为左子树CBD和右子树GFE，因此左子树后序为CDB，右子树后序为GFE。左子树根为B，中序CBD中C在B左侧、D在B右侧，左子树先序为BCD。右子树根为E，中序GFE中GF都在E左侧；该左子树后序为GF，根为F，G是F的左孩子，故右子树先序为EFG。整树先序为A+BCD+EFG，即ABCDEFG，与选项A一致。选项B、C、D均把左子树先序BCD错误写成BDC，选项C、D还改变了右子树的先序顺序。易错点是混淆中序和先序的结点顺序。复习时应先由后序确定根，再按中序划分子树并递归处理。</t>
+        </is>
+      </c>
+      <c r="O19" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P19" s="7" t="inlineStr">
+        <is>
+          <t>AI 内容复核修订：原答案 C/解析拼接错误；非真人审核签字。原始生成记录保留。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -1890,7 +1978,7 @@
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>某排序算法在每一趟结束后，都能保证至少有一个元素被放置到其最终位置上。下列哪种排序算法一定不具备这一性质？</t>
+          <t>对互异关键字升序排序，按教材常规完整一趟定义：冒泡排序将当前无序区最大值移到末端，简单选择排序选最小值，快速排序采用一趟后将枢轴置于最终位置的分区法。下列哪种算法不保证每趟结束至少有一个元素到达最终位置？</t>
         </is>
       </c>
       <c r="I20" s="7" t="inlineStr">
@@ -1920,11 +2008,19 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>正确答案是D。直接插入排序在每一趟中只是将当前元素插入到前面已排好序的子序列中，已有序子序列中的元素位置仍可能因后续元素的插入而整体后移，因此不能保证每趟至少有一个元素到达最终位置。冒泡排序每趟可将最大或最小元素送到最终位置，快速排序每趟划分可将枢轴元素放到最终位置，简单选择排序每趟可选择最小元素放到最终位置，三者均具备该性质。常见易错点是把“局部有序”误认为“最终位置确定”，复习时应重点区分各排序算法每趟操作后元素位置的确定性。</t>
-        </is>
-      </c>
-      <c r="O20" s="8" t="n"/>
-      <c r="P20" s="7" t="n"/>
+          <t>正确答案为D。直接插入排序每趟只让已处理的前缀有序，后续插入仍可改变这些元素的位置。例如[3,2,1]第一趟变为[2,3,1]，最终为[1,2,3]，此时三个位置都未最终确定。B项冒泡每趟固定最大值，C项选择每趟固定最小值；A项按题目限定的分区法每趟固定枢轴。注意这一结论依赖题目给出的快速排序分区实现，不适用于所有分区方案。易错点是把局部有序当成最终就位，复习时用具体反例检验保证性命题。</t>
+        </is>
+      </c>
+      <c r="O20" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；改为不保证，并限定关键字互异、完整一趟和枢轴定位分区。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -1960,7 +2056,7 @@
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>对序列 (5, 3, 5', 2) 进行排序，其中 5 与 5' 的关键字相同，5 在 5' 之前。若要求排序后 5 仍排在 5' 之前，则下列排序算法中一定不能满足要求的是？</t>
+          <t>排序稳定性指相等关键字元素在排序前后的相对次序保持不变。采用常规实现：冒泡仅逆序时交换，插入仅后移严格大于待插入关键字的元素，归并时相等优先取左侧，堆排序直接以关键字比较而不附加原始位置。下列哪种算法不能保证对任意输入都稳定？</t>
         </is>
       </c>
       <c r="I21" s="7" t="inlineStr">
@@ -1990,11 +2086,19 @@
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>正确答案是B。堆排序在调整堆的过程中可能将关键字相同的元素交换到相对次序相反的位置，因此是不稳定排序，无法保证排序后 5 仍位于 5' 之前。直接插入排序、归并排序和冒泡排序都是稳定排序，在关键字相等时不会改变元素的相对次序。常见易错点是把“时间复杂度为O(nlogn)”与“稳定”混为一谈，误认为归并排序和堆排序都稳定。复习建议是熟记常见排序算法的稳定性：稳定的有插入、冒泡、归并、基数排序；不稳定的有选择、快速、希尔、堆排序。</t>
-        </is>
-      </c>
-      <c r="O21" s="8" t="n"/>
-      <c r="P21" s="7" t="n"/>
+          <t>正确答案为B。常规堆排序的建堆与首尾交换可能改变相等关键字的相对次序，因此不能对所有输入保证稳定；这并不表示每个输入都会逆序。A项冒泡只交换严格逆序对，等值元素不会越过彼此；C项插入只后移严格较大元素，新等值元素留在已有等值元素之后；D项归并相等优先取左，结合稳定的递归子排序可保持原次序。易错点是把存在破坏稳定性的反例误解为每次都失败，复习时应区分不能保证与必然逆序。</t>
+        </is>
+      </c>
+      <c r="O21" s="8" t="inlineStr">
+        <is>
+          <t>修改后通过</t>
+        </is>
+      </c>
+      <c r="P21" s="7" t="inlineStr">
+        <is>
+          <t>AI内容预审修订，非真人审核签字；改问任意输入的稳定性保证，明确相等关键字实现，去掉具体输入一定失败。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="0" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="0" deleteRows="0" formatCells="0" formatRows="0" sort="0"/>
